--- a/_trackers/Ticker_Company_Names.xlsx
+++ b/_trackers/Ticker_Company_Names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugit\Documents\Claude\_Stock_agent\_trackers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EA7D05-9D13-4D14-92C4-8455852677AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F000B9CC-B4D5-41B1-B426-614D961B5D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1009,7 +1009,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1025,6 +1025,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1057,7 +1081,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1079,6 +1103,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1101,13 +1142,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>388620</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -1435,14 +1476,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1450,253 +1491,255 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="10" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="14" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="10" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="10" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="D12" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="14" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="D15" s="10" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="14" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="D17" s="14" t="s">
+        <v>315</v>
+      </c>
       <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="D19" s="4"/>
       <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="D20" s="4"/>
       <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="15" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="15" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
@@ -1704,16 +1747,16 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
@@ -1721,16 +1764,16 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
@@ -1738,63 +1781,60 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
@@ -1802,7 +1842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>72</v>
       </c>
@@ -1810,7 +1850,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>74</v>
       </c>
@@ -1818,7 +1858,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
@@ -1826,7 +1866,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>78</v>
       </c>
@@ -1834,7 +1874,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
@@ -1842,7 +1882,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>82</v>
       </c>
@@ -1850,7 +1890,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>84</v>
       </c>
@@ -1858,7 +1898,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>86</v>
       </c>
@@ -1866,7 +1906,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>88</v>
       </c>
@@ -1874,7 +1914,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>90</v>
       </c>
@@ -1882,7 +1922,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
@@ -1890,7 +1930,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
@@ -1898,7 +1938,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
@@ -1906,7 +1946,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>98</v>
       </c>
@@ -1914,7 +1954,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>100</v>
       </c>
@@ -1922,7 +1962,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
@@ -1930,7 +1970,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
@@ -1938,7 +1978,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>106</v>
       </c>
@@ -1946,7 +1986,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>108</v>
       </c>
@@ -1954,7 +1994,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>110</v>
       </c>
@@ -1962,7 +2002,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
@@ -1970,7 +2010,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>114</v>
       </c>
@@ -1978,160 +2018,160 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F59" s="4"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F60" s="4"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E60" s="4"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E61" s="4"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F62" s="4"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E62" s="4"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F63" s="4"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E63" s="4"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F64" s="4"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F65" s="4"/>
-    </row>
-    <row r="66" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E65" s="4"/>
+    </row>
+    <row r="66" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F66" s="5"/>
-    </row>
-    <row r="67" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E66" s="5"/>
+    </row>
+    <row r="67" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F67" s="6"/>
-    </row>
-    <row r="68" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E67" s="6"/>
+    </row>
+    <row r="68" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E68" s="6"/>
+    </row>
+    <row r="69" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E69" s="6"/>
+    </row>
+    <row r="70" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F70" s="5"/>
-    </row>
-    <row r="71" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E70" s="5"/>
+    </row>
+    <row r="71" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E71" s="6"/>
+    </row>
+    <row r="72" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="5"/>
-    </row>
-    <row r="73" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E72" s="5"/>
+    </row>
+    <row r="73" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F74" s="8"/>
-    </row>
-    <row r="75" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="E74" s="8"/>
+    </row>
+    <row r="75" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E75" s="7"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>150</v>
       </c>
@@ -2139,7 +2179,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>152</v>
       </c>
@@ -2147,7 +2187,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>154</v>
       </c>
@@ -2155,7 +2195,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>156</v>
       </c>
@@ -2163,7 +2203,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>158</v>
       </c>
@@ -2741,21 +2781,21 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" display="https://claude.ai/chat/bfb4ac80-377e-4583-8a3b-e36898fa4621" xr:uid="{196CDD08-B680-4FEC-9BF2-B20F2CB2938A}"/>
-    <hyperlink ref="E4" r:id="rId2" display="https://claude.ai/chat/b341063a-6693-4bdf-9444-4778d7b24904" xr:uid="{28C0163E-9A67-40A4-A313-C23EF817EE02}"/>
-    <hyperlink ref="E6" r:id="rId3" display="https://claude.ai/chat/730270ef-dda9-494f-b007-c992a90f5a40" xr:uid="{E2AE3247-9423-472B-BDDD-D108B862CD07}"/>
-    <hyperlink ref="E7" r:id="rId4" display="https://claude.ai/chat/1ad27010-30a8-4540-8de4-84557a4e8df9" xr:uid="{BBD89F30-7362-4033-9AE4-093F4D87B7FC}"/>
-    <hyperlink ref="E8" r:id="rId5" display="https://claude.ai/chat/efa63240-eb21-4d5c-8498-cf4fcaaa96ee" xr:uid="{953FD1C3-3D11-419C-96AF-093D2942A9D1}"/>
-    <hyperlink ref="E9" r:id="rId6" display="https://claude.ai/chat/9bf1732b-5457-4428-923e-97e5cae96a32" xr:uid="{3FE095A5-395F-49EE-A866-E8D6F45E0F9A}"/>
-    <hyperlink ref="E12" r:id="rId7" display="https://claude.ai/chat/f17639c4-ff73-4843-a89c-e95841f62cc0" xr:uid="{5600CDF8-1F29-4E0B-A315-2C39D0708E4B}"/>
-    <hyperlink ref="E13" r:id="rId8" display="https://claude.ai/chat/1f8d268a-98ec-48e6-9c5a-f98e009364f8" xr:uid="{7A6EDA41-FEE8-45E8-99FC-F75B980A114B}"/>
-    <hyperlink ref="E14" r:id="rId9" display="https://claude.ai/chat/53d3f6d0-8add-4533-a44f-e0a0aac989ff" xr:uid="{A16FC0FA-5049-435B-938A-508478716E25}"/>
-    <hyperlink ref="E15" r:id="rId10" display="https://claude.ai/chat/b7c00c2e-56e3-4932-b7dc-cbf7f5b565c4" xr:uid="{EB66547A-4A83-4EC3-A792-A941BDB5627B}"/>
-    <hyperlink ref="E16" r:id="rId11" display="https://claude.ai/chat/6ce0b116-44b6-4d97-a932-70dfcc5ba16d" xr:uid="{F0177972-8625-4B22-B468-A3317374436E}"/>
-    <hyperlink ref="E31" r:id="rId12" display="https://claude.ai/chat/89c72186-457a-422c-8647-bb9f43644e7a" xr:uid="{D7525A0A-D516-4EA6-A07A-C4F1E44362E3}"/>
-    <hyperlink ref="E5" r:id="rId13" display="https://claude.ai/chat/86c0b6f1-35f1-4ce9-b258-4af4e25b832b" xr:uid="{A993253F-E1A7-4423-BCCB-87CDEADCC36A}"/>
-    <hyperlink ref="E10" r:id="rId14" display="https://claude.ai/chat/235beb67-ac44-4603-9d9f-52070e99d0c1" xr:uid="{AD4C6E5C-3F89-41BF-A1BC-EC283DA7717E}"/>
-    <hyperlink ref="E11" r:id="rId15" display="https://claude.ai/chat/5108fdd1-25cd-45b7-b27b-ab4634b95b0a" xr:uid="{DFF544C3-BEAB-40F3-BA1C-55B775C8FBC2}"/>
+    <hyperlink ref="D3" r:id="rId1" display="https://claude.ai/chat/bfb4ac80-377e-4583-8a3b-e36898fa4621" xr:uid="{196CDD08-B680-4FEC-9BF2-B20F2CB2938A}"/>
+    <hyperlink ref="D4" r:id="rId2" display="https://claude.ai/chat/b341063a-6693-4bdf-9444-4778d7b24904" xr:uid="{28C0163E-9A67-40A4-A313-C23EF817EE02}"/>
+    <hyperlink ref="D6" r:id="rId3" display="https://claude.ai/chat/730270ef-dda9-494f-b007-c992a90f5a40" xr:uid="{E2AE3247-9423-472B-BDDD-D108B862CD07}"/>
+    <hyperlink ref="D7" r:id="rId4" display="https://claude.ai/chat/1ad27010-30a8-4540-8de4-84557a4e8df9" xr:uid="{BBD89F30-7362-4033-9AE4-093F4D87B7FC}"/>
+    <hyperlink ref="D8" r:id="rId5" display="https://claude.ai/chat/efa63240-eb21-4d5c-8498-cf4fcaaa96ee" xr:uid="{953FD1C3-3D11-419C-96AF-093D2942A9D1}"/>
+    <hyperlink ref="D9" r:id="rId6" display="https://claude.ai/chat/9bf1732b-5457-4428-923e-97e5cae96a32" xr:uid="{3FE095A5-395F-49EE-A866-E8D6F45E0F9A}"/>
+    <hyperlink ref="D12" r:id="rId7" display="https://claude.ai/chat/f17639c4-ff73-4843-a89c-e95841f62cc0" xr:uid="{5600CDF8-1F29-4E0B-A315-2C39D0708E4B}"/>
+    <hyperlink ref="D13" r:id="rId8" display="https://claude.ai/chat/1f8d268a-98ec-48e6-9c5a-f98e009364f8" xr:uid="{7A6EDA41-FEE8-45E8-99FC-F75B980A114B}"/>
+    <hyperlink ref="D14" r:id="rId9" display="https://claude.ai/chat/53d3f6d0-8add-4533-a44f-e0a0aac989ff" xr:uid="{A16FC0FA-5049-435B-938A-508478716E25}"/>
+    <hyperlink ref="D15" r:id="rId10" display="https://claude.ai/chat/b7c00c2e-56e3-4932-b7dc-cbf7f5b565c4" xr:uid="{EB66547A-4A83-4EC3-A792-A941BDB5627B}"/>
+    <hyperlink ref="D16" r:id="rId11" display="https://claude.ai/chat/6ce0b116-44b6-4d97-a932-70dfcc5ba16d" xr:uid="{F0177972-8625-4B22-B468-A3317374436E}"/>
+    <hyperlink ref="D17" r:id="rId12" display="https://claude.ai/chat/89c72186-457a-422c-8647-bb9f43644e7a" xr:uid="{D7525A0A-D516-4EA6-A07A-C4F1E44362E3}"/>
+    <hyperlink ref="D5" r:id="rId13" display="https://claude.ai/chat/86c0b6f1-35f1-4ce9-b258-4af4e25b832b" xr:uid="{A993253F-E1A7-4423-BCCB-87CDEADCC36A}"/>
+    <hyperlink ref="D10" r:id="rId14" display="https://claude.ai/chat/235beb67-ac44-4603-9d9f-52070e99d0c1" xr:uid="{AD4C6E5C-3F89-41BF-A1BC-EC283DA7717E}"/>
+    <hyperlink ref="D11" r:id="rId15" display="https://claude.ai/chat/5108fdd1-25cd-45b7-b27b-ab4634b95b0a" xr:uid="{DFF544C3-BEAB-40F3-BA1C-55B775C8FBC2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId16"/>

--- a/_trackers/Ticker_Company_Names.xlsx
+++ b/_trackers/Ticker_Company_Names.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugit\Documents\Claude\_Stock_agent\_trackers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F000B9CC-B4D5-41B1-B426-614D961B5D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BEE9798-245A-474D-964D-F31D6EC509E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1081,13 +1081,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1498,7 +1497,7 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1507,7 +1506,7 @@
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>301</v>
       </c>
     </row>
@@ -1518,18 +1517,18 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="13" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>303</v>
       </c>
     </row>
@@ -1540,69 +1539,69 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="3"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -1611,10 +1610,10 @@
       <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -1623,30 +1622,30 @@
       <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="13" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>313</v>
       </c>
     </row>
@@ -1657,21 +1656,21 @@
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="13" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="E17" s="4"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1680,31 +1679,31 @@
       <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="14" t="s">
         <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -1712,17 +1711,17 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -1736,8 +1735,8 @@
       <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -1754,7 +1753,7 @@
       <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
@@ -1771,7 +1770,7 @@
       <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -1788,7 +1787,7 @@
       <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="4"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -1805,7 +1804,7 @@
       <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="4"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
@@ -1814,7 +1813,7 @@
       <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="4"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
@@ -1823,7 +1822,7 @@
       <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -1832,7 +1831,7 @@
       <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="4"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
@@ -2025,7 +2024,7 @@
       <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E59" s="4"/>
+      <c r="E59" s="3"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
@@ -2034,7 +2033,7 @@
       <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E60" s="4"/>
+      <c r="E60" s="3"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
@@ -2043,7 +2042,7 @@
       <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="E61" s="4"/>
+      <c r="E61" s="3"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
@@ -2052,7 +2051,7 @@
       <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E62" s="4"/>
+      <c r="E62" s="3"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
@@ -2061,7 +2060,7 @@
       <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E63" s="4"/>
+      <c r="E63" s="3"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -2070,7 +2069,7 @@
       <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E64" s="4"/>
+      <c r="E64" s="3"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
@@ -2079,7 +2078,7 @@
       <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E65" s="4"/>
+      <c r="E65" s="3"/>
     </row>
     <row r="66" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
@@ -2088,7 +2087,7 @@
       <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="4"/>
     </row>
     <row r="67" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
@@ -2097,7 +2096,7 @@
       <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="6"/>
+      <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
@@ -2106,7 +2105,7 @@
       <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E68" s="6"/>
+      <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
@@ -2115,7 +2114,7 @@
       <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E69" s="6"/>
+      <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
@@ -2124,7 +2123,7 @@
       <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E70" s="5"/>
+      <c r="E70" s="4"/>
     </row>
     <row r="71" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
@@ -2133,7 +2132,7 @@
       <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E71" s="6"/>
+      <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
@@ -2142,7 +2141,7 @@
       <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="E72" s="5"/>
+      <c r="E72" s="4"/>
     </row>
     <row r="73" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
@@ -2151,7 +2150,7 @@
       <c r="B73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="7"/>
+      <c r="E73" s="6"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
@@ -2160,7 +2159,7 @@
       <c r="B74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E74" s="8"/>
+      <c r="E74" s="7"/>
     </row>
     <row r="75" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
@@ -2169,7 +2168,7 @@
       <c r="B75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E75" s="7"/>
+      <c r="E75" s="6"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
